--- a/stories/arbres/TREE-SOC-008.xlsx
+++ b/stories/arbres/TREE-SOC-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est dans le salon avec maman. On va sortir. Dans la voiture, Hugo reste assis. Assis, avec l'adulte. Maman est l'adulte. Papa range les sacs. Les pieds de Hugo restent sur le tapis de la place.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|On parle du bac à sable. Une feuille tombe. Puis la voiture. Hugo reste assis. Assis avec l'adulte. Maman est à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la voiture, Hugo fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -2005,6 +2042,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Assis. Avec l'adulte. Hugo a retenu. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2233,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2357,6 +2404,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose les cubes sur ses genoux. Ça sent l'herbe coupée. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2545,6 +2597,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2713,6 +2770,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. On entend un oiseau. On pensait au bac à sable. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2937,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3108,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Ça sent l'herbe coupée. On pensait au bac à sable. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3275,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3446,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Le soleil chauffe un peu. On pensait au bac à sable. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3613,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3784,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose le livre sur ses genoux. Le soleil chauffe un peu. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3885,6 +3977,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4053,6 +4150,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. Ça sent l'herbe coupée. On pensait au bac à sable. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4215,6 +4317,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4381,6 +4488,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Le soleil chauffe un peu. On pensait au bac à sable. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4543,6 +4655,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4709,6 +4826,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Le sol est frais. On pensait au bac à sable. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4871,6 +4993,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5037,6 +5164,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose la dînette sur ses genoux. Le sol est frais. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5225,6 +5357,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5393,6 +5530,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. Le soleil chauffe un peu. On pensait au bac à sable. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5555,6 +5697,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5721,6 +5868,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Le sol est frais. On pensait au bac à sable. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5883,6 +6035,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6049,6 +6206,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Un petit bruit d'eau. On pensait au bac à sable. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6211,6 +6373,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6377,6 +6544,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|On parle du toboggan. Le vent est doux. Puis la voiture. Hugo reste assis. Assis avec l'adulte. Maman est à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6557,6 +6729,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la voiture, Hugo fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6729,6 +6906,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Assis. Avec l'adulte. Hugo a retenu. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6915,6 +7097,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7081,6 +7268,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose les cubes sur ses genoux. Ça sent l'herbe coupée. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7269,6 +7461,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7437,6 +7634,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. Ça sent l'herbe coupée. On pensait au toboggan. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7599,6 +7801,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7765,6 +7972,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Le soleil chauffe un peu. On pensait au toboggan. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7927,6 +8139,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8093,6 +8310,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Le sol est frais. On pensait au toboggan. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8255,6 +8477,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8421,6 +8648,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose le livre sur ses genoux. Le soleil chauffe un peu. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8609,6 +8841,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8777,6 +9014,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. Le soleil chauffe un peu. On pensait au toboggan. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8939,6 +9181,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9105,6 +9352,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Le sol est frais. On pensait au toboggan. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9267,6 +9519,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9433,6 +9690,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Un petit bruit d'eau. On pensait au toboggan. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9595,6 +9857,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9761,6 +10028,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose la dînette sur ses genoux. Le sol est frais. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9949,6 +10221,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10117,6 +10394,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. Le sol est frais. On pensait au toboggan. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10279,6 +10561,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10445,6 +10732,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Un petit bruit d'eau. On pensait au toboggan. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10607,6 +10899,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10773,6 +11070,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Les chaussures font toc toc. On pensait au toboggan. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10935,6 +11237,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11101,6 +11408,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|On parle des balançoires. On entend un oiseau. Puis la voiture. Hugo reste assis. Assis avec l'adulte. Maman est à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11281,6 +11593,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la voiture, Hugo fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -11453,6 +11770,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Assis. Avec l'adulte. Hugo a retenu. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11639,6 +11961,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11805,6 +12132,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose les cubes sur ses genoux. Ça sent l'herbe coupée. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11993,6 +12325,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12161,6 +12498,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. Le soleil chauffe un peu. On pensait aux balançoires. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12323,6 +12665,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12489,6 +12836,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Le sol est frais. On pensait aux balançoires. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12651,6 +13003,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12817,6 +13174,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Un petit bruit d'eau. On pensait aux balançoires. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12979,6 +13341,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13145,6 +13512,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose le livre sur ses genoux. Le soleil chauffe un peu. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13333,6 +13705,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13501,6 +13878,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. Le sol est frais. On pensait aux balançoires. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13663,6 +14045,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13829,6 +14216,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Un petit bruit d'eau. On pensait aux balançoires. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13991,6 +14383,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14157,6 +14554,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Les chaussures font toc toc. On pensait aux balançoires. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14319,6 +14721,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14485,6 +14892,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo pose la dînette sur ses genoux. Le sol est frais. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14673,6 +15085,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14841,6 +15258,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac rouge sur les genoux. Un petit bruit d'eau. On pensait aux balançoires. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15003,6 +15425,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15169,6 +15596,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac bleu sur les genoux. Les chaussures font toc toc. On pensait aux balançoires. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15331,6 +15763,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15497,6 +15934,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a le sac vert sur les genoux. Un vélo passe au loin. On pensait aux balançoires. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15659,6 +16101,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15677,7 +16124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15750,6 +16197,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-008.xlsx
+++ b/stories/arbres/TREE-SOC-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Hugo est dans le salon avec maman. On va sortir. Dans la voiture, Hugo reste assis. Assis, avec l'adulte. Maman est l'adulte. Papa range les sacs. Les pieds de Hugo restent sur le tapis de la place.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|On parle du bac à sable. Une feuille tombe. Puis la voiture. Hugo reste assis. Assis avec l'adulte. Maman est à côté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|Dans la voiture, Hugo fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2047,6 +2056,7 @@
           <t>narrateur|Oui. Assis. Avec l'adulte. Hugo a retenu. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2238,6 +2248,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2409,6 +2420,7 @@
           <t>narrateur|Hugo pose les cubes sur ses genoux. Ça sent l'herbe coupée. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2604,6 +2616,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2775,6 +2788,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. On entend un oiseau. On pensait au bac à sable. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2942,6 +2956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3113,6 +3128,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Ça sent l'herbe coupée. On pensait au bac à sable. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3280,6 +3296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3451,6 +3468,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Le soleil chauffe un peu. On pensait au bac à sable. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3618,6 +3636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3789,6 +3808,7 @@
           <t>narrateur|Hugo pose le livre sur ses genoux. Le soleil chauffe un peu. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3984,6 +4004,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4155,6 +4176,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. Ça sent l'herbe coupée. On pensait au bac à sable. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4322,6 +4344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4493,6 +4516,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Le soleil chauffe un peu. On pensait au bac à sable. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4660,6 +4684,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4831,6 +4856,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Le sol est frais. On pensait au bac à sable. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4998,6 +5024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5169,6 +5196,7 @@
           <t>narrateur|Hugo pose la dînette sur ses genoux. Le sol est frais. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5364,6 +5392,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5535,6 +5564,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. Le soleil chauffe un peu. On pensait au bac à sable. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5702,6 +5732,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5873,6 +5904,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Le sol est frais. On pensait au bac à sable. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6040,6 +6072,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6211,6 +6244,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Un petit bruit d'eau. On pensait au bac à sable. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6378,6 +6412,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6549,6 +6584,7 @@
           <t>narrateur|On parle du toboggan. Le vent est doux. Puis la voiture. Hugo reste assis. Assis avec l'adulte. Maman est à côté.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6736,6 +6772,7 @@
           <t>narrateur|Dans la voiture, Hugo fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6911,6 +6948,7 @@
           <t>narrateur|Oui. Assis. Avec l'adulte. Hugo a retenu. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7102,6 +7140,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7273,6 +7312,7 @@
           <t>narrateur|Hugo pose les cubes sur ses genoux. Ça sent l'herbe coupée. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7468,6 +7508,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7639,6 +7680,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. Ça sent l'herbe coupée. On pensait au toboggan. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7806,6 +7848,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7977,6 +8020,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Le soleil chauffe un peu. On pensait au toboggan. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8144,6 +8188,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8315,6 +8360,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Le sol est frais. On pensait au toboggan. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8482,6 +8528,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8653,6 +8700,7 @@
           <t>narrateur|Hugo pose le livre sur ses genoux. Le soleil chauffe un peu. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8848,6 +8896,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9019,6 +9068,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. Le soleil chauffe un peu. On pensait au toboggan. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9186,6 +9236,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9357,6 +9408,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Le sol est frais. On pensait au toboggan. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9524,6 +9576,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9695,6 +9748,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Un petit bruit d'eau. On pensait au toboggan. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9862,6 +9916,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10033,6 +10088,7 @@
           <t>narrateur|Hugo pose la dînette sur ses genoux. Le sol est frais. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10228,6 +10284,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10399,6 +10456,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. Le sol est frais. On pensait au toboggan. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10566,6 +10624,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10737,6 +10796,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Un petit bruit d'eau. On pensait au toboggan. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10904,6 +10964,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11075,6 +11136,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Les chaussures font toc toc. On pensait au toboggan. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11242,6 +11304,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11413,6 +11476,7 @@
           <t>narrateur|On parle des balançoires. On entend un oiseau. Puis la voiture. Hugo reste assis. Assis avec l'adulte. Maman est à côté.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11600,6 +11664,7 @@
           <t>narrateur|Dans la voiture, Hugo fait quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11775,6 +11840,7 @@
           <t>narrateur|Oui. Assis. Avec l'adulte. Hugo a retenu. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11966,6 +12032,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12137,6 +12204,7 @@
           <t>narrateur|Hugo pose les cubes sur ses genoux. Ça sent l'herbe coupée. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12332,6 +12400,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12503,6 +12572,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. Le soleil chauffe un peu. On pensait aux balançoires. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12670,6 +12740,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12841,6 +12912,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Le sol est frais. On pensait aux balançoires. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13008,6 +13080,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13179,6 +13252,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Un petit bruit d'eau. On pensait aux balançoires. Les cubes sont posés. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13346,6 +13420,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13517,6 +13592,7 @@
           <t>narrateur|Hugo pose le livre sur ses genoux. Le soleil chauffe un peu. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13712,6 +13788,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13883,6 +13960,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. Le sol est frais. On pensait aux balançoires. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14050,6 +14128,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14221,6 +14300,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Un petit bruit d'eau. On pensait aux balançoires. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14388,6 +14468,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14559,6 +14640,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Les chaussures font toc toc. On pensait aux balançoires. Le livre est posé. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14726,6 +14808,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14897,6 +14980,7 @@
           <t>narrateur|Hugo pose la dînette sur ses genoux. Le sol est frais. Hugo reste assis. Avec l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15092,6 +15176,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15263,6 +15348,7 @@
           <t>narrateur|Hugo a le sac rouge sur les genoux. Un petit bruit d'eau. On pensait aux balançoires. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15430,6 +15516,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15601,6 +15688,7 @@
           <t>narrateur|Hugo a le sac bleu sur les genoux. Les chaussures font toc toc. On pensait aux balançoires. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15768,6 +15856,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15939,6 +16028,7 @@
           <t>narrateur|Hugo a le sac vert sur les genoux. Un vélo passe au loin. On pensait aux balançoires. La dînette est posée. Hugo reste assis. Avec l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16106,6 +16196,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16124,7 +16215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16204,6 +16295,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16218,7 +16323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16405,6 +16510,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
